--- a/ig/nr/resolveISConflict/StructureDefinition-mes-observation-glucose.xlsx
+++ b/ig/nr/resolveISConflict/StructureDefinition-mes-observation-glucose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-22T15:44:50+00:00</t>
+    <t>2023-03-22T16:12:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
